--- a/2_rate_fitting/inputs/PRISM_nmr_rates.xlsx
+++ b/2_rate_fitting/inputs/PRISM_nmr_rates.xlsx
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>7.091</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="67">
